--- a/ru/downloads/data-excel/1.3.1.a.xlsx
+++ b/ru/downloads/data-excel/1.3.1.a.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66221209-FCD1-4284-BD12-4B8D3D27DB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
-    <t>1.3.1.1c Доля граждан, получающих пенсии/ЕСП</t>
-  </si>
-  <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
   <si>
@@ -38,12 +36,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>1.3.1.1c Proportion of senior citizens receiving pensions / CAP.</t>
-  </si>
-  <si>
-    <t>1.3.1.1с Пенсия/АСЖ алган улгайган жарандардын үлүшү</t>
-  </si>
-  <si>
     <t>Доля населения, получающих пенсии</t>
   </si>
   <si>
@@ -59,9 +51,6 @@
     <t>АСЖ алган калктын үлүшү</t>
   </si>
   <si>
-    <t>Социалдык пособие алган калктын пайызы</t>
-  </si>
-  <si>
     <t>Percentage of the population receiving pensions</t>
   </si>
   <si>
@@ -78,21 +67,42 @@
   </si>
   <si>
     <t>(in percent)</t>
+  </si>
+  <si>
+    <t>1.3.1.a Proportion of senior citizens receiving pensions / CAP.</t>
+  </si>
+  <si>
+    <t>1.3.1.a Доля граждан, получающих пенсии/ЕСП</t>
+  </si>
+  <si>
+    <t>Социалдык жөлөкпул алган калктын пайызы</t>
+  </si>
+  <si>
+    <t>1.3.1.a Пенсия/АСЖ алган улгайган жарандардын үлүшү</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,78 +183,82 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Normal 2" xfId="1"/>
+  <cellStyles count="4">
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{EF4B1512-D95F-41FC-8764-D2FD91CDBDCC}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -521,8 +535,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="36.28515625" style="5" customWidth="1"/>
@@ -530,15 +544,15 @@
     <col min="21" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
@@ -556,35 +570,35 @@
       <c r="Q1" s="3"/>
       <c r="R1" s="3"/>
     </row>
-    <row r="2" spans="1:20" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-    </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -605,16 +619,17 @@
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U3" s="22"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>3</v>
       </c>
       <c r="D4" s="7">
         <v>2007</v>
@@ -667,16 +682,19 @@
       <c r="T4" s="7">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="19">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" s="12">
         <v>10.1</v>
@@ -729,16 +747,19 @@
       <c r="T5" s="12">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="21">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" s="13">
         <v>8.2777821713499495</v>
@@ -791,16 +812,19 @@
       <c r="T6" s="12">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U6" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D7" s="15">
         <v>1.1240260959130568</v>
@@ -853,8 +877,11 @@
       <c r="T7" s="16">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U7" s="20">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -874,13 +901,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="P9" s="8"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -900,7 +927,7 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -920,7 +947,7 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
